--- a/downloads/forms/resume.xlsx
+++ b/downloads/forms/resume.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="이력서" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'이력서'!$A$1:$O$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'이력서'!$A$1:$O$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O33"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.78947368421053" customWidth="1" min="1" max="1"/>
@@ -712,7 +712,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="20.40944881889764" customHeight="1">
+    <row r="8" ht="18.70866141732284" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>기 간</t>
@@ -745,7 +745,7 @@
       </c>
       <c r="O8" s="5" t="n"/>
     </row>
-    <row r="9" ht="20.40944881889764" customHeight="1">
+    <row r="9" ht="18.70866141732284" customHeight="1">
       <c r="A9" s="6" t="n"/>
       <c r="B9" s="7" t="n"/>
       <c r="C9" s="5" t="n"/>
@@ -762,7 +762,7 @@
       <c r="N9" s="6" t="n"/>
       <c r="O9" s="5" t="n"/>
     </row>
-    <row r="10" ht="20.40944881889764" customHeight="1">
+    <row r="10" ht="18.70866141732284" customHeight="1">
       <c r="A10" s="6" t="n"/>
       <c r="B10" s="7" t="n"/>
       <c r="C10" s="5" t="n"/>
@@ -779,7 +779,7 @@
       <c r="N10" s="6" t="n"/>
       <c r="O10" s="5" t="n"/>
     </row>
-    <row r="11" ht="20.40944881889764" customHeight="1">
+    <row r="11" ht="18.70866141732284" customHeight="1">
       <c r="A11" s="6" t="n"/>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="5" t="n"/>
@@ -796,71 +796,71 @@
       <c r="N11" s="6" t="n"/>
       <c r="O11" s="5" t="n"/>
     </row>
-    <row r="12" ht="20.40944881889764" customHeight="1">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="6" t="n"/>
-      <c r="O12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>구분: 졸업 · 졸업 예정 · 재학 · 수료 · 중퇴</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>경력 사항</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="20.40944881889764" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="14" ht="18.70866141732284" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>기 간</t>
         </is>
       </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>회사명</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>부서 · 직위</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>담당 업무</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="n"/>
+      <c r="N14" s="7" t="n"/>
+      <c r="O14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="18.70866141732284" customHeight="1">
+      <c r="A15" s="6" t="n"/>
       <c r="B15" s="7" t="n"/>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>회사명</t>
-        </is>
-      </c>
+      <c r="D15" s="6" t="n"/>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="5" t="n"/>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>부서 · 직위</t>
-        </is>
-      </c>
+      <c r="G15" s="6" t="n"/>
       <c r="H15" s="7" t="n"/>
       <c r="I15" s="7" t="n"/>
       <c r="J15" s="7" t="n"/>
       <c r="K15" s="5" t="n"/>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>담당 업무</t>
-        </is>
-      </c>
+      <c r="L15" s="6" t="n"/>
       <c r="M15" s="7" t="n"/>
       <c r="N15" s="7" t="n"/>
       <c r="O15" s="5" t="n"/>
     </row>
-    <row r="16" ht="20.40944881889764" customHeight="1">
+    <row r="16" ht="18.70866141732284" customHeight="1">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="7" t="n"/>
       <c r="C16" s="5" t="n"/>
@@ -877,7 +877,7 @@
       <c r="N16" s="7" t="n"/>
       <c r="O16" s="5" t="n"/>
     </row>
-    <row r="17" ht="20.40944881889764" customHeight="1">
+    <row r="17" ht="18.70866141732284" customHeight="1">
       <c r="A17" s="6" t="n"/>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="5" t="n"/>
@@ -894,7 +894,7 @@
       <c r="N17" s="7" t="n"/>
       <c r="O17" s="5" t="n"/>
     </row>
-    <row r="18" ht="20.40944881889764" customHeight="1">
+    <row r="18" ht="18.70866141732284" customHeight="1">
       <c r="A18" s="6" t="n"/>
       <c r="B18" s="7" t="n"/>
       <c r="C18" s="5" t="n"/>
@@ -911,60 +911,60 @@
       <c r="N18" s="7" t="n"/>
       <c r="O18" s="5" t="n"/>
     </row>
-    <row r="19" ht="20.40944881889764" customHeight="1">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="n"/>
-      <c r="J19" s="7" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="6" t="n"/>
-      <c r="M19" s="7" t="n"/>
-      <c r="N19" s="7" t="n"/>
-      <c r="O19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>자격 · 면허 · 어학</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="20.40944881889764" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="20" ht="18.70866141732284" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>취득일</t>
         </is>
       </c>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>자격증 · 시험명</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="7" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>발행 기관 · 점수</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="n"/>
+      <c r="L20" s="7" t="n"/>
+      <c r="M20" s="7" t="n"/>
+      <c r="N20" s="7" t="n"/>
+      <c r="O20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="18.70866141732284" customHeight="1">
+      <c r="A21" s="6" t="n"/>
       <c r="B21" s="7" t="n"/>
       <c r="C21" s="5" t="n"/>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>자격증 · 시험명</t>
-        </is>
-      </c>
+      <c r="D21" s="6" t="n"/>
       <c r="E21" s="7" t="n"/>
       <c r="F21" s="7" t="n"/>
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="7" t="n"/>
       <c r="I21" s="5" t="n"/>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>발행 기관 · 점수</t>
-        </is>
-      </c>
+      <c r="J21" s="6" t="n"/>
       <c r="K21" s="7" t="n"/>
       <c r="L21" s="7" t="n"/>
       <c r="M21" s="7" t="n"/>
       <c r="N21" s="7" t="n"/>
       <c r="O21" s="5" t="n"/>
     </row>
-    <row r="22" ht="20.40944881889764" customHeight="1">
+    <row r="22" ht="18.70866141732284" customHeight="1">
       <c r="A22" s="6" t="n"/>
       <c r="B22" s="7" t="n"/>
       <c r="C22" s="5" t="n"/>
@@ -981,7 +981,7 @@
       <c r="N22" s="7" t="n"/>
       <c r="O22" s="5" t="n"/>
     </row>
-    <row r="23" ht="20.40944881889764" customHeight="1">
+    <row r="23" ht="18.70866141732284" customHeight="1">
       <c r="A23" s="6" t="n"/>
       <c r="B23" s="7" t="n"/>
       <c r="C23" s="5" t="n"/>
@@ -998,43 +998,47 @@
       <c r="N23" s="7" t="n"/>
       <c r="O23" s="5" t="n"/>
     </row>
-    <row r="24" ht="20.40944881889764" customHeight="1">
-      <c r="A24" s="6" t="n"/>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="6" t="n"/>
-      <c r="K24" s="7" t="n"/>
-      <c r="L24" s="7" t="n"/>
-      <c r="M24" s="7" t="n"/>
-      <c r="N24" s="7" t="n"/>
-      <c r="O24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>교육 · 활동 · 수상</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="20.40944881889764" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="25" ht="18.70866141732284" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>기 간</t>
         </is>
       </c>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>내 용</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="7" t="n"/>
+      <c r="J25" s="7" t="n"/>
+      <c r="K25" s="7" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>기 관</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="n"/>
+      <c r="O25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="18.70866141732284" customHeight="1">
+      <c r="A26" s="6" t="n"/>
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="5" t="n"/>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>내 용</t>
-        </is>
-      </c>
+      <c r="D26" s="6" t="n"/>
       <c r="E26" s="7" t="n"/>
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="7" t="n"/>
@@ -1043,15 +1047,11 @@
       <c r="J26" s="7" t="n"/>
       <c r="K26" s="7" t="n"/>
       <c r="L26" s="5" t="n"/>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>기 관</t>
-        </is>
-      </c>
+      <c r="M26" s="6" t="n"/>
       <c r="N26" s="7" t="n"/>
       <c r="O26" s="5" t="n"/>
     </row>
-    <row r="27" ht="20.40944881889764" customHeight="1">
+    <row r="27" ht="18.70866141732284" customHeight="1">
       <c r="A27" s="6" t="n"/>
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="5" t="n"/>
@@ -1068,52 +1068,60 @@
       <c r="N27" s="7" t="n"/>
       <c r="O27" s="5" t="n"/>
     </row>
-    <row r="28" ht="20.40944881889764" customHeight="1">
-      <c r="A28" s="6" t="n"/>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
-      <c r="I28" s="7" t="n"/>
-      <c r="J28" s="7" t="n"/>
-      <c r="K28" s="7" t="n"/>
-      <c r="L28" s="5" t="n"/>
-      <c r="M28" s="6" t="n"/>
-      <c r="N28" s="7" t="n"/>
-      <c r="O28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>병역 사항</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="20.40944881889764" customHeight="1">
+    <row r="29" ht="18.70866141732284" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>구 분</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>군 별</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="7" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>계 급</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="n"/>
+      <c r="M29" s="7" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="18.70866141732284" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>구 분</t>
+          <t>복무 기간</t>
         </is>
       </c>
       <c r="B30" s="6" t="n"/>
       <c r="C30" s="7" t="n"/>
       <c r="D30" s="7" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>군 별</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="6" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="7" t="n"/>
       <c r="I30" s="7" t="n"/>
       <c r="J30" s="5" t="n"/>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>계 급</t>
+          <t>면제 사유</t>
         </is>
       </c>
       <c r="L30" s="7" t="n"/>
@@ -1121,67 +1129,45 @@
       <c r="N30" s="5" t="n"/>
       <c r="O30" s="6" t="n"/>
     </row>
-    <row r="31" ht="20.40944881889764" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>복무 기간</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="7" t="n"/>
-      <c r="I31" s="7" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="4" t="inlineStr">
-        <is>
-          <t>면제 사유</t>
-        </is>
-      </c>
-      <c r="L31" s="7" t="n"/>
-      <c r="M31" s="7" t="n"/>
-      <c r="N31" s="5" t="n"/>
-      <c r="O31" s="6" t="n"/>
-    </row>
-    <row r="32" ht="29.33858267716536" customHeight="1">
-      <c r="A32" s="14" t="inlineStr">
+    <row r="31" ht="29.33858267716536" customHeight="1">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>위에 적은 내용은 사실과 다름이 없습니다.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="23.66929133858268" customHeight="1">
-      <c r="A33" s="15" t="inlineStr">
+    <row r="32" ht="23.66929133858268" customHeight="1">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">        년      월      일            작성자 :                       (인)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="89">
-    <mergeCell ref="A25:O25"/>
+  <mergeCells count="85">
     <mergeCell ref="N11:O11"/>
+    <mergeCell ref="F29:G29"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="A12:O12"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="L17:O17"/>
     <mergeCell ref="D11:H11"/>
     <mergeCell ref="A32:O32"/>
-    <mergeCell ref="L19:O19"/>
-    <mergeCell ref="A29:O29"/>
+    <mergeCell ref="D14:F14"/>
     <mergeCell ref="G15:K15"/>
     <mergeCell ref="L3:O3"/>
     <mergeCell ref="A13:O13"/>
-    <mergeCell ref="H30:J30"/>
     <mergeCell ref="D26:L26"/>
+    <mergeCell ref="A31:O31"/>
+    <mergeCell ref="D20:I20"/>
     <mergeCell ref="I8:M8"/>
+    <mergeCell ref="H29:J29"/>
     <mergeCell ref="D9:H9"/>
+    <mergeCell ref="L14:O14"/>
     <mergeCell ref="I2:K2"/>
+    <mergeCell ref="A24:O24"/>
     <mergeCell ref="D22:I22"/>
     <mergeCell ref="G16:K16"/>
     <mergeCell ref="I10:M10"/>
@@ -1194,63 +1180,56 @@
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="I11:M11"/>
     <mergeCell ref="E5:O5"/>
-    <mergeCell ref="A12:C12"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="F30:G30"/>
     <mergeCell ref="E4:O4"/>
     <mergeCell ref="E3:H3"/>
+    <mergeCell ref="A14:C14"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="L16:O16"/>
     <mergeCell ref="M26:O26"/>
-    <mergeCell ref="I12:M12"/>
-    <mergeCell ref="A20:O20"/>
+    <mergeCell ref="A28:O28"/>
+    <mergeCell ref="G14:K14"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="B29:E29"/>
     <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="D27:L27"/>
     <mergeCell ref="A18:C18"/>
+    <mergeCell ref="M25:O25"/>
     <mergeCell ref="I3:K3"/>
+    <mergeCell ref="J20:O20"/>
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="G17:K17"/>
-    <mergeCell ref="D28:L28"/>
-    <mergeCell ref="A33:O33"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="D18:F18"/>
     <mergeCell ref="J22:O22"/>
-    <mergeCell ref="G19:K19"/>
     <mergeCell ref="K30:N30"/>
+    <mergeCell ref="D25:L25"/>
+    <mergeCell ref="A20:C20"/>
     <mergeCell ref="N8:O8"/>
+    <mergeCell ref="B30:J30"/>
     <mergeCell ref="J21:O21"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="D24:I24"/>
+    <mergeCell ref="A19:O19"/>
+    <mergeCell ref="K29:N29"/>
     <mergeCell ref="N10:O10"/>
     <mergeCell ref="J23:O23"/>
     <mergeCell ref="L18:O18"/>
     <mergeCell ref="N9:O9"/>
-    <mergeCell ref="K31:N31"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="A1:O1"/>
-    <mergeCell ref="J24:O24"/>
-    <mergeCell ref="B30:E30"/>
     <mergeCell ref="A27:C27"/>
     <mergeCell ref="A2:B5"/>
     <mergeCell ref="M27:O27"/>
     <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A14:O14"/>
     <mergeCell ref="A17:C17"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="G18:K18"/>
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A19:C19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="D23:I23"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="L15:O15"/>
-    <mergeCell ref="D19:F19"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="B31:J31"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5905511811023623" right="0.5905511811023623" top="0.5905511811023623" bottom="0.5905511811023623" header="0.2" footer="0.2"/>
